--- a/DateBase/orders/Dang Nguyen48_2026-10-22.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-10-22.xlsx
@@ -1189,6 +1189,9 @@
       <c r="G2" t="str">
         <v>0555555555520555555753355559555151510151010161077201316351529816525101261055121511156512101010583555131010101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
